--- a/resources/Programmes/programmeclasseCP.xlsx
+++ b/resources/Programmes/programmeclasseCP.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colyl\Documents\Alymia\Gestion scolaire\Back\Gestion-Scolaire\resources\Programmes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Feuille 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="152">
   <si>
     <t>Matière</t>
   </si>
@@ -488,41 +496,46 @@
   <si>
     <t>Évaluation des exercices écrits
 Observation</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -532,57 +545,62 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -772,17 +790,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AA35"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -829,7 +850,7 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -858,7 +879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
@@ -884,7 +905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
@@ -910,7 +931,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
@@ -936,7 +957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>37</v>
       </c>
@@ -962,7 +983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>42</v>
       </c>
@@ -988,7 +1009,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>48</v>
       </c>
@@ -1014,7 +1035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
@@ -1043,7 +1064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>61</v>
       </c>
@@ -1069,10 +1090,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>66</v>
       </c>
+      <c r="B13" s="5" t="s">
+        <v>151</v>
+      </c>
       <c r="C13" s="5" t="s">
         <v>67</v>
       </c>
@@ -1095,7 +1119,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>74</v>
       </c>
@@ -1112,10 +1136,10 @@
         <v>78</v>
       </c>
       <c r="F15" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>79</v>
@@ -1124,7 +1148,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>81</v>
       </c>
@@ -1142,7 +1166,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>85</v>
       </c>
@@ -1171,7 +1195,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>93</v>
       </c>
@@ -1197,7 +1221,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>99</v>
       </c>
@@ -1223,7 +1247,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>104</v>
       </c>
@@ -1249,7 +1273,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>109</v>
       </c>
@@ -1275,10 +1299,13 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>116</v>
       </c>
+      <c r="B25" t="s">
+        <v>151</v>
+      </c>
       <c r="C25" s="7" t="s">
         <v>117</v>
       </c>
@@ -1302,10 +1329,13 @@
       </c>
       <c r="J25" s="5"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>121</v>
       </c>
+      <c r="B27" t="s">
+        <v>151</v>
+      </c>
       <c r="C27" s="5" t="s">
         <v>122</v>
       </c>
@@ -1328,7 +1358,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1338,7 +1368,7 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>126</v>
       </c>
@@ -1355,10 +1385,10 @@
         <v>130</v>
       </c>
       <c r="F29" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>131</v>
@@ -1367,7 +1397,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
         <v>132</v>
       </c>
@@ -1385,7 +1415,7 @@
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>136</v>
       </c>
@@ -1402,10 +1432,10 @@
         <v>140</v>
       </c>
       <c r="F32" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>141</v>
@@ -1414,7 +1444,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
         <v>142</v>
       </c>
@@ -1432,10 +1462,13 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>146</v>
       </c>
+      <c r="B35" s="5" t="s">
+        <v>151</v>
+      </c>
       <c r="C35" s="5" t="s">
         <v>147</v>
       </c>
@@ -1459,6 +1492,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resources/Programmes/programmeclasseCP.xlsx
+++ b/resources/Programmes/programmeclasseCP.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colyl\Documents\Alymia\Gestion scolaire\Back\Gestion-Scolaire\resources\Programmes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\gestionscolaire\resources\Programmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="155">
   <si>
     <t>Matière</t>
   </si>
@@ -232,9 +232,6 @@
   <si>
     <t>1. Parcours de motricité
 2. Jeux collectifs (chaises musicales)</t>
-  </si>
-  <si>
-    <t>2 heures</t>
   </si>
   <si>
     <t>1 heure</t>
@@ -499,6 +496,18 @@
   </si>
   <si>
     <t>NULL</t>
+  </si>
+  <si>
+    <t>1heure</t>
+  </si>
+  <si>
+    <t>2 heure</t>
+  </si>
+  <si>
+    <t>heure_debut</t>
+  </si>
+  <si>
+    <t>heure_fin</t>
   </si>
 </sst>
 </file>
@@ -800,10 +809,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="11" width="18.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -829,10 +847,14 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -849,8 +871,10 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+    </row>
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -876,10 +900,19 @@
         <v>16</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
       <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
@@ -902,10 +935,19 @@
         <v>23</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>150</v>
+      </c>
       <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
@@ -928,10 +970,19 @@
         <v>30</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>150</v>
+      </c>
       <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
@@ -954,10 +1005,19 @@
         <v>35</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
       <c r="B6" s="5" t="s">
         <v>37</v>
       </c>
@@ -980,10 +1040,19 @@
         <v>41</v>
       </c>
       <c r="I6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
       <c r="B7" s="5" t="s">
         <v>42</v>
       </c>
@@ -1006,10 +1075,19 @@
         <v>46</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
       <c r="B8" s="5" t="s">
         <v>48</v>
       </c>
@@ -1032,24 +1110,65 @@
         <v>52</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="B9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>22</v>
@@ -1058,437 +1177,574 @@
         <v>15</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>150</v>
+      </c>
       <c r="B11" s="5" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="5">
+        <v>30</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="G18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="5" t="s">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="G19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="5">
         <v>30</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H22" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>109</v>
+        <v>150</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="5">
+        <v>30</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="114" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="H26" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K26" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="5"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F29" s="5">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5">
-        <v>30</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="5">
-        <v>1</v>
-      </c>
-      <c r="G32" s="5">
-        <v>30</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
